--- a/Equipments/Transport_to_Aachen/DACNV_Equipment_List_輸送分類.xlsx
+++ b/Equipments/Transport_to_Aachen/DACNV_Equipment_List_輸送分類.xlsx
@@ -13,7 +13,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'機材一覧'!$A$4:$E$57</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'機材一覧'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'輸送分類'!$A$4:$N$57</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'輸送分類'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -870,7 +872,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5" customHeight="1"/>
@@ -2478,7 +2480,17 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:E57"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2486,7 +2498,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6063,7 +6075,17 @@
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -6071,7 +6093,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8186,7 +8208,17 @@
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -8194,7 +8226,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8400,6 +8432,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Equipments/Transport_to_Aachen/DACNV_Equipment_List_輸送分類.xlsx
+++ b/Equipments/Transport_to_Aachen/DACNV_Equipment_List_輸送分類.xlsx
@@ -2482,7 +2482,7 @@
   <autoFilter ref="A4:E57"/>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
@@ -2504,19 +2504,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="62" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6077,7 +6077,7 @@
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
@@ -6098,15 +6098,15 @@
   <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8232,7 +8232,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -8249,7 +8249,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6">
       <c r="B6" s="43" t="inlineStr">
         <is>
           <t>どちらも「規則上は持込可能、実務上は保安検査の裁量が唯一の障壁」。レーザーは準備次第で通る見込み、マイクロ波アンプはほぼ問題なく通る。ただし乗継便のため、出発地・経由国・ドイツの3回の保安検査を通ることになり、経由国が最も読みにくい。</t>
@@ -8263,77 +8263,77 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9">
       <c r="B9" s="43" t="inlineStr">
         <is>
           <t>・危険物該当性：DPSSレーザーでリチウム電池も高圧ガスも含まないため、IATA危険物規則上は該当なし。この点で持込を妨げる規則は存在しない。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10">
       <c r="B10" s="43" t="inlineStr">
         <is>
           <t>・実際の障壁：保安検査官が「高出力レーザーポインタ」と判断した場合の任意放棄要求。300mW/532nm はクラス3Bにあたり、国によっては一般人の所持が規制される出力帯にあるため、研究機材であることをその場で示せるかが分かれ目になる。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11">
       <c r="B11" s="43" t="inlineStr">
         <is>
           <t>・準備すべきもの（すべて英文・紙で携行）：</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
+    <row r="12">
       <c r="B12" s="43" t="inlineStr">
         <is>
           <t>・所属機関発行の英文レター（研究目的、渡航先の受入機関名、機材名と型番を明記）</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13">
       <c r="B13" s="43" t="inlineStr">
         <is>
           <t>・メーカー仕様書（波長・出力・クラス分類が読み取れるページ）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14">
       <c r="B14" s="43" t="inlineStr">
         <is>
           <t>・受入側（ドイツ）研究室からの受入証明またはメール printout</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15">
       <c r="B15" s="43" t="inlineStr">
         <is>
           <t>・購入証明・インボイス（一時輸出であること、再輸入予定を示せると望ましい）</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16">
       <c r="B16" s="43" t="inlineStr">
         <is>
           <t>・レーザー保護メガネ（研究用途であることの傍証になる）</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17">
       <c r="B17" s="43" t="inlineStr">
         <is>
           <t>・運用上のコツ：ヘッドと電源部を分けて機内持込バッグの取り出しやすい位置に入れ、検査時に自分から申告して書類を出す。黙って通そうとすると心証が悪く不利になる。また、機内での通電・動作は絶対にしないこと。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="45" customHeight="1">
+    <row r="18">
       <c r="B18" s="43" t="inlineStr">
         <is>
           <t>・輸出管理：別表第1第6項（貨物等省令第6条）の対象カテゴリ。CW 532nm・300mW は規制のしきい値を下回り非該当となる公算が大きいが、これは推定であり、CNI に該非判定書（パラメータシート）を必ず請求すること。手荷物での持出も輸出に当たるため、発送であれ持参であれ該非判定は同じく必要。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19">
       <c r="B19" s="43" t="inlineStr">
         <is>
           <t>・実現性の評価：準備を揃えれば十分に現実的。ただし経由国での没収リスクはゼロにできないため、「万一失った場合に現地で代替をレンタル／購入できるか」を事前に受入研究室と確認しておくと安全。</t>
@@ -8347,35 +8347,35 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
+    <row r="22">
       <c r="B22" s="43" t="inlineStr">
         <is>
           <t>・危険物該当性：電池・ガスを含まない受動的な金属筐体の電子機器で、該当なし。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23">
       <c r="B23" s="43" t="inlineStr">
         <is>
           <t>・実際の障壁：ほぼない。密度の高い金属塊なのでX線画像で不透明に写り、開披検査になる可能性は高いが、蓋を開けて仕様書を見せれば通る。重量2kg前後で手荷物重量制限内。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
+    <row r="24">
       <c r="B24" s="43" t="inlineStr">
         <is>
           <t>・準備すべきもの：メーカーのデータシート（英文）と、レーザーと同じ所属機関レター。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
+    <row r="25">
       <c r="B25" s="43" t="inlineStr">
         <is>
           <t>・輸出管理：別表第1第9項（貨物等省令第8条）。増幅器は動作周波数帯と出力によって該当し得るため、Mini-Circuits から該非判定書または ECCN の回答を取ること（要確認）。</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
+    <row r="26">
       <c r="B26" s="43" t="inlineStr">
         <is>
           <t>・実現性の評価：高い。レーザーより優先度を下げてよい。</t>
@@ -8389,28 +8389,28 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
+    <row r="29">
       <c r="B29" s="43" t="inlineStr">
         <is>
           <t>・信号発生器 Windfreak SynthHD：広帯域シンセサイザで、本リスト中もっとも第9項該当のリスクが高い。輸送の可否ではなく輸出許可の要否が問題になるため、該非判定書の取得を最優先で進めること。該当すると判定された場合、発送・持参いずれでも経済産業大臣の許可が必要になり、取得に数週間かかるのでスケジュールに影響する。</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
+    <row r="30">
       <c r="B30" s="43" t="inlineStr">
         <is>
           <t>・ベリリウム銅DAC：ベリリウム合金は含有率次第で別表第1第2項の対象になり得る。借用元に材質証明（Be含有率）を確認すること。</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
+    <row r="31">
       <c r="B31" s="43" t="inlineStr">
         <is>
           <t>・アラルダイト：接着剤は硬化剤側が危険物に該当し得るため持込・預入とも不可。現地調達が現実的。</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="45" customHeight="1">
+    <row r="32">
       <c r="B32" s="43" t="inlineStr">
         <is>
           <t>・電源電圧：日本の100V機（DC電源 PWR401L、はんだごて、LEDドライバー用電源）はドイツの230Vでそのまま使えない。変圧器を用意するか、現地で230V対応品を調達する方が結果的に安く済む場合がある。</t>
@@ -8424,7 +8424,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35">
       <c r="B35" s="43" t="inlineStr">
         <is>
           <t>本メモの輸出令項番はいずれも公開仕様からの推定であり、該非判定の最終結論ではない。申請にあたっては各メーカーの該非判定書を取得し、所属機関の輸出管理担当部署の確認を受けること。航空会社の持込可否も最終的には当日の運送人および保安当局の判断による。</t>
